--- a/Teststdplan_ohne_Makros.xlsx
+++ b/Teststdplan_ohne_Makros.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4cfeafcae5aef467/visual studios/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="65" documentId="8_{EEB25A61-9672-4442-9B6E-899A645A90B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D0FD0863-BABB-4D5D-8CB2-2745A842A50E}"/>
+  <xr:revisionPtr revIDLastSave="66" documentId="8_{EEB25A61-9672-4442-9B6E-899A645A90B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{87E799F3-2B0F-4170-95D7-0FABBD48BF23}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2730" windowWidth="31455" windowHeight="19935" tabRatio="926" activeTab="3" xr2:uid="{C94283D1-368C-4DD4-A799-AF02E78A3071}"/>
+    <workbookView xWindow="22200" yWindow="11295" windowWidth="31455" windowHeight="19935" tabRatio="926" activeTab="2" xr2:uid="{C94283D1-368C-4DD4-A799-AF02E78A3071}"/>
   </bookViews>
   <sheets>
     <sheet name="UV" sheetId="2" r:id="rId1"/>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18240" uniqueCount="2307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18241" uniqueCount="2308">
   <si>
     <t>U-Nr</t>
   </si>
@@ -7035,6 +7035,9 @@
   </si>
   <si>
     <t>Strafe zu wenig NuHo</t>
+  </si>
+  <si>
+    <t>gilt nicht für fixierte Doppelstunden</t>
   </si>
 </sst>
 </file>
@@ -7243,6 +7246,10 @@
     <xdr:clientData/>
   </xdr:oneCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -68879,6 +68886,16 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A17:H17"/>
+    <mergeCell ref="A182:H182"/>
+    <mergeCell ref="A186:H186"/>
+    <mergeCell ref="A190:H190"/>
+    <mergeCell ref="A194:H194"/>
+    <mergeCell ref="A359:H359"/>
     <mergeCell ref="A544:H544"/>
     <mergeCell ref="A548:H548"/>
     <mergeCell ref="A363:H363"/>
@@ -68886,16 +68903,6 @@
     <mergeCell ref="A371:H371"/>
     <mergeCell ref="A536:H536"/>
     <mergeCell ref="A540:H540"/>
-    <mergeCell ref="A182:H182"/>
-    <mergeCell ref="A186:H186"/>
-    <mergeCell ref="A190:H190"/>
-    <mergeCell ref="A194:H194"/>
-    <mergeCell ref="A359:H359"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A5:H5"/>
-    <mergeCell ref="A9:H9"/>
-    <mergeCell ref="A13:H13"/>
-    <mergeCell ref="A17:H17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
 </worksheet>
@@ -70758,6 +70765,9 @@
       <c r="B28" s="12" t="s">
         <v>1684</v>
       </c>
+      <c r="C28" s="11" t="s">
+        <v>2307</v>
+      </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
